--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_60.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_60.xlsx
@@ -767,14 +767,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_41.jpg</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>stimuli/key/key_12.jpg</t>
@@ -787,12 +787,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
         <v>9</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
       </c>
       <c r="W4" t="n">
         <v>15</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
         <v>13</v>
@@ -965,12 +965,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
         <v>15</v>
@@ -1059,17 +1059,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
         <v>13</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>7</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1328,13 +1328,13 @@
         <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1356,42 +1356,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_41.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_34.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_34.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
         <v>10</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,16 +1523,16 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V11" t="n">
         <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1622,7 +1622,7 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1730,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
         <v>16</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2021,7 +2021,7 @@
         <v>15</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2117,10 +2117,10 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_37.jpg</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_40.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_40.jpg</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_37.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_05.jpg</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2216,16 +2216,16 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U18" t="n">
         <v>7</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2252,19 +2252,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_05.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_25.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_25.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -2272,17 +2272,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2318,13 +2318,13 @@
         <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
         <v>18</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2414,10 +2414,10 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
         <v>4</v>
@@ -2445,14 +2445,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_19.jpg</t>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2513,10 +2513,10 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" t="n">
         <v>5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>10</v>
       </c>
       <c r="V21" t="n">
         <v>12</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2612,7 +2612,7 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
         <v>4</v>
@@ -2653,14 +2653,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_40.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>chair</t>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2717,10 +2717,10 @@
         <v>8</v>
       </c>
       <c r="V23" t="n">
+        <v>3</v>
+      </c>
+      <c r="W23" t="n">
         <v>6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2912,13 +2912,13 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
         <v>18</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3008,13 +3008,13 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>16</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>18</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
         <v>15</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
         <v>13</v>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3407,10 +3407,10 @@
         <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
         <v>15</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>4</v>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3701,10 +3701,10 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
         <v>17</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3800,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
         <v>7</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3902,7 +3902,7 @@
         <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
         <v>8</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_41.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_02.jpg</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>stimuli/key/key_12.jpg</t>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3998,10 +3998,10 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
         <v>10</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>15</v>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V37" t="n">
         <v>18</v>
       </c>
       <c r="W37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4196,7 +4196,7 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U38" t="n">
         <v>1</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4304,7 +4304,7 @@
         <v>8</v>
       </c>
       <c r="W39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>18</v>
       </c>
       <c r="W40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>15</v>
       </c>
       <c r="V41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W41" t="n">
         <v>12</v>
@@ -4529,14 +4529,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_37.jpg</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_34.jpg</t>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4595,10 +4595,10 @@
         <v>15</v>
       </c>
       <c r="U42" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" t="n">
         <v>9</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5</v>
       </c>
       <c r="W42" t="n">
         <v>16</v>
@@ -4623,17 +4623,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4643,17 +4643,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4691,13 +4691,13 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4790,7 +4790,7 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U44" t="n">
         <v>7</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W45" t="n">
         <v>4</v>
@@ -4920,17 +4920,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4988,13 +4988,13 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
         <v>12</v>
@@ -5019,14 +5019,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>stimuli/key/key_28.jpg</t>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5087,10 +5087,10 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
+        <v>9</v>
+      </c>
+      <c r="U47" t="n">
         <v>5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>10</v>
       </c>
       <c r="V47" t="n">
         <v>15</v>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,7 +5186,7 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
         <v>4</v>
@@ -5195,7 +5195,7 @@
         <v>18</v>
       </c>
       <c r="W48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5227,14 +5227,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_37.jpg</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>chair</t>
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5291,10 +5291,10 @@
         <v>8</v>
       </c>
       <c r="V49" t="n">
+        <v>2</v>
+      </c>
+      <c r="W49" t="n">
         <v>9</v>
-      </c>
-      <c r="W49" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5390,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="V50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W50" t="n">
         <v>12</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5486,13 +5486,13 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V51" t="n">
         <v>12</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
         <v>16</v>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>12</v>
       </c>
       <c r="V53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
         <v>18</v>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5981,10 +5981,10 @@
         <v>8</v>
       </c>
       <c r="U56" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6077,13 +6077,13 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
         <v>4</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W57" t="n">
         <v>13</v>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6179,10 +6179,10 @@
         <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W58" t="n">
         <v>1</v>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6275,10 +6275,10 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
         <v>7</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6374,7 +6374,7 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
         <v>7</v>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W61" t="n">
         <v>15</v>
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_41.jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_36.jpg</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
         <v>10</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
+        <v>2</v>
+      </c>
+      <c r="W62" t="n">
         <v>3</v>
-      </c>
-      <c r="V62" t="n">
-        <v>9</v>
-      </c>
-      <c r="W62" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6671,10 +6671,10 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V63" t="n">
         <v>17</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,7 +6770,7 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U64" t="n">
         <v>1</v>
@@ -6779,7 +6779,7 @@
         <v>18</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>18</v>
       </c>
       <c r="W66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>15</v>
       </c>
       <c r="V67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W67" t="n">
         <v>12</v>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7169,13 +7169,13 @@
         <v>15</v>
       </c>
       <c r="U68" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
         <v>4</v>
       </c>
       <c r="W68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -7197,17 +7197,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7265,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W69" t="n">
         <v>16</v>
@@ -7296,42 +7296,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_37.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_40.jpg</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_37.jpg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_40.jpg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_05.jpg</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7364,16 +7364,16 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U70" t="n">
         <v>7</v>
       </c>
       <c r="V70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7466,7 +7466,7 @@
         <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V71" t="n">
         <v>8</v>
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_05.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_25.jpg</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_37.jpg</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_25.jpg</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U72" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V72" t="n">
         <v>18</v>
       </c>
       <c r="W72" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_28.jpg</t>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7661,10 +7661,10 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
+        <v>9</v>
+      </c>
+      <c r="U73" t="n">
         <v>5</v>
-      </c>
-      <c r="U73" t="n">
-        <v>10</v>
       </c>
       <c r="V73" t="n">
         <v>1</v>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7760,7 +7760,7 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U74" t="n">
         <v>4</v>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7868,7 +7868,7 @@
         <v>12</v>
       </c>
       <c r="W75" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8060,13 +8060,13 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V77" t="n">
         <v>18</v>
       </c>
       <c r="W77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
         <v>16</v>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8555,10 +8555,10 @@
         <v>8</v>
       </c>
       <c r="U82" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W82" t="n">
         <v>15</v>
@@ -8583,19 +8583,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_34.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_34.jpg</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_41.jpg</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_05.jpg</t>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8651,13 +8651,13 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U83" t="n">
         <v>4</v>
       </c>
       <c r="V83" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W83" t="n">
         <v>13</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8753,7 +8753,7 @@
         <v>4</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V84" t="n">
         <v>17</v>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8849,10 +8849,10 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V85" t="n">
         <v>7</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U86" t="n">
         <v>7</v>
       </c>
       <c r="V86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W86" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9050,13 +9050,13 @@
         <v>7</v>
       </c>
       <c r="U87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V87" t="n">
         <v>17</v>
       </c>
       <c r="W87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_41.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_12.jpg</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_12.jpg</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>5</v>
+      </c>
+      <c r="U88" t="n">
         <v>10</v>
-      </c>
-      <c r="U88" t="n">
-        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>15</v>
       </c>
       <c r="W88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_02.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U89" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V89" t="n">
         <v>18</v>
       </c>
       <c r="W89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_41.jpg</t>
+          <t>stimuli/house/house_36.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_04.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9344,13 +9344,13 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
       <c r="V90" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W90" t="n">
         <v>7</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/dog/dog_41.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9452,7 +9452,7 @@
         <v>17</v>
       </c>
       <c r="W91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>15</v>
       </c>
       <c r="V93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W93" t="n">
         <v>12</v>
@@ -9677,19 +9677,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_37.jpg</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_05.jpg</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>key</t>
@@ -9697,17 +9697,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9743,13 +9743,13 @@
         <v>15</v>
       </c>
       <c r="U94" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V94" t="n">
+        <v>10</v>
+      </c>
+      <c r="W94" t="n">
         <v>3</v>
-      </c>
-      <c r="W94" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9839,10 +9839,10 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U95" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V95" t="n">
         <v>1</v>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U96" t="n">
         <v>7</v>
       </c>
       <c r="V96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W96" t="n">
         <v>16</v>
@@ -9974,17 +9974,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9994,17 +9994,17 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10040,13 +10040,13 @@
         <v>7</v>
       </c>
       <c r="U97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W97" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10136,10 +10136,10 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V98" t="n">
         <v>4</v>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_27.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10187,17 +10187,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10235,13 +10235,13 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
+        <v>9</v>
+      </c>
+      <c r="U99" t="n">
         <v>5</v>
       </c>
-      <c r="U99" t="n">
-        <v>10</v>
-      </c>
       <c r="V99" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W99" t="n">
         <v>7</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_37.jpg</t>
+          <t>stimuli/dog/dog_37.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10334,7 +10334,7 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U100" t="n">
         <v>4</v>
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_40.jpg</t>
+          <t>stimuli/jacket/jacket_37.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
+          <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10439,10 +10439,10 @@
         <v>8</v>
       </c>
       <c r="V101" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -10568,19 +10568,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_40.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_25.jpg</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_05.jpg</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_25.jpg</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_27.jpg</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>ball</t>
@@ -10588,17 +10588,17 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10634,13 +10634,13 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V103" t="n">
         <v>18</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_05.jpg</t>
+          <t>stimuli/bread/bread_40.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U104" t="n">
         <v>16</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_37.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>12</v>
       </c>
       <c r="V105" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W105" t="n">
         <v>18</v>
